--- a/TouchGFX/assets/texts/texts.xlsx
+++ b/TouchGFX/assets/texts/texts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-button-example\ButtonExample\assets\texts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-flex-button-example\FlexButtonExample\assets\texts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
   <si>
     <t>Font</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Default</t>
   </si>
   <si>
-    <t>TextId1</t>
-  </si>
-  <si>
     <t>0-9</t>
   </si>
   <si>
@@ -163,7 +160,67 @@
     <t>Left</t>
   </si>
   <si>
-    <t>0</t>
+    <t>SingleUseId2</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>ButtonDown</t>
+  </si>
+  <si>
+    <t>SingleUseId3</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>SingleUseId5</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>SingleUseId6</t>
+  </si>
+  <si>
+    <t>SingleUseId7</t>
+  </si>
+  <si>
+    <t>SingleUseId8</t>
+  </si>
+  <si>
+    <t>Repeat Button</t>
+  </si>
+  <si>
+    <t>Click Button</t>
+  </si>
+  <si>
+    <t>Touch Button</t>
+  </si>
+  <si>
+    <t>-+,.</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>numberText</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>toggleButtonWhite</t>
+  </si>
+  <si>
+    <t>toggleButtonOrange</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Toggle Button (touch text)</t>
   </si>
   <si>
     <t>Column1</t>
@@ -1396,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>8</v>
@@ -1410,7 +1467,7 @@
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1419,10 +1476,12 @@
         <v>4</v>
       </c>
       <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="24"/>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J4" s="24"/>
       <c r="L4" s="4" t="s">
@@ -1442,6 +1501,25 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
       <c r="L5" s="7" t="s">
         <v>1</v>
       </c>
@@ -1457,6 +1535,25 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
       <c r="L6" s="7" t="s">
         <v>2</v>
       </c>
@@ -1560,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J5"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.28515625" customWidth="1"/>
@@ -1598,62 +1695,198 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
       </c>
       <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
-        <v>44</v>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/TouchGFX/assets/texts/texts.xlsx
+++ b/TouchGFX/assets/texts/texts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-flex-button-example\FlexButtonExample\assets\texts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-slider-example\SliderExample\assets\texts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t>Font</t>
   </si>
@@ -31,18 +31,36 @@
     <t>Bpp</t>
   </si>
   <si>
+    <t>Alignment</t>
+  </si>
+  <si>
     <t>GB</t>
   </si>
   <si>
     <t>TouchGFX - Typography Sheet</t>
   </si>
   <si>
+    <t>Text ID</t>
+  </si>
+  <si>
     <t>TouchGFX - Translation Sheet</t>
   </si>
   <si>
     <t>Typography Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Add additional language here (1 to 3 capital letters) - </t>
+  </si>
+  <si>
+    <t>Add additional language here (1 to 3 capital letters) - 2</t>
+  </si>
+  <si>
+    <t>Add additional language here (1 to 3 capital letters) - 3</t>
+  </si>
+  <si>
+    <t>Add additional language here (1 to 3 capital letters) - 4</t>
+  </si>
+  <si>
     <t>Add additional language columns here</t>
   </si>
   <si>
@@ -122,114 +140,6 @@
   </si>
   <si>
     <t>0x22EF</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>0-9</t>
-  </si>
-  <si>
-    <t>&lt;number&gt;</t>
-  </si>
-  <si>
-    <t>Asap-Regular.ttf</t>
-  </si>
-  <si>
-    <t>TEXT ID</t>
-  </si>
-  <si>
-    <t>TYPOGRAPHY NAME</t>
-  </si>
-  <si>
-    <t>ALIGNMENT</t>
-  </si>
-  <si>
-    <t>DIRECTION</t>
-  </si>
-  <si>
-    <t>Center</t>
-  </si>
-  <si>
-    <t>LTR</t>
-  </si>
-  <si>
-    <t>SingleUseId1</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>SingleUseId2</t>
-  </si>
-  <si>
-    <t>DOWN</t>
-  </si>
-  <si>
-    <t>ButtonDown</t>
-  </si>
-  <si>
-    <t>SingleUseId3</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>SingleUseId5</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>SingleUseId6</t>
-  </si>
-  <si>
-    <t>SingleUseId7</t>
-  </si>
-  <si>
-    <t>SingleUseId8</t>
-  </si>
-  <si>
-    <t>Repeat Button</t>
-  </si>
-  <si>
-    <t>Click Button</t>
-  </si>
-  <si>
-    <t>Touch Button</t>
-  </si>
-  <si>
-    <t>-+,.</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>numberText</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>toggleButtonWhite</t>
-  </si>
-  <si>
-    <t>toggleButtonOrange</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>Toggle Button (touch text)</t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
   </si>
   <si>
     <t>Widget Wildcard Characters</t>
@@ -1008,14 +918,14 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="B3:I799" totalsRowShown="0" tableBorderDxfId="0">
   <tableColumns count="8">
-    <tableColumn id="1" name="TEXT ID"/>
-    <tableColumn id="2" name="TYPOGRAPHY NAME"/>
-    <tableColumn id="3" name="ALIGNMENT"/>
+    <tableColumn id="1" name="Text ID"/>
+    <tableColumn id="2" name="Typography Name"/>
+    <tableColumn id="3" name="Alignment"/>
     <tableColumn id="4" name="GB"/>
-    <tableColumn id="5" name="DIRECTION"/>
-    <tableColumn id="6" name="Column1"/>
-    <tableColumn id="7" name="Column2"/>
-    <tableColumn id="8" name="Column3"/>
+    <tableColumn id="5" name="Add additional language here (1 to 3 capital letters) - "/>
+    <tableColumn id="6" name="Add additional language here (1 to 3 capital letters) - 2"/>
+    <tableColumn id="7" name="Add additional language here (1 to 3 capital letters) - 3"/>
+    <tableColumn id="8" name="Add additional language here (1 to 3 capital letters) - 4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1422,7 +1332,7 @@
     </row>
     <row r="2" spans="2:16" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -1435,7 +1345,7 @@
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>0</v>
@@ -1447,84 +1357,57 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="24"/>
-      <c r="G4" t="s">
-        <v>59</v>
-      </c>
+      <c r="G4" s="24"/>
       <c r="H4" s="24"/>
-      <c r="I4" t="s">
-        <v>35</v>
-      </c>
+      <c r="I4" s="24"/>
       <c r="J4" s="24"/>
       <c r="L4" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5">
-        <v>27</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
       <c r="L5" s="7" t="s">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N5" s="9">
         <v>20</v>
@@ -1535,30 +1418,15 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
       <c r="L6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N6" s="9">
         <v>4</v>
@@ -1570,65 +1438,65 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L7" s="7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L8" s="7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L9" s="11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L10" s="11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P10" s="14"/>
     </row>
@@ -1637,7 +1505,7 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="M12" s="16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1657,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J13"/>
+  <dimension ref="B1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.28515625" customWidth="1"/>
@@ -1680,7 +1548,7 @@
     </row>
     <row r="2" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -1690,205 +1558,37 @@
       <c r="H2" s="23"/>
       <c r="I2" s="23"/>
       <c r="J2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
-        <v>41</v>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-    </row>
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <mergeCells count="1">

--- a/TouchGFX/assets/texts/texts.xlsx
+++ b/TouchGFX/assets/texts/texts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-slider-example\SliderExample\assets\texts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-slide-menu-example\SlideMenuExample\assets\texts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/TouchGFX/assets/texts/texts.xlsx
+++ b/TouchGFX/assets/texts/texts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-slide-menu-example\SlideMenuExample\assets\texts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git_workspace\packages\TGUI\ui-flex-button-example\FlexButtonExample\assets\texts\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
   <si>
     <t>Font</t>
   </si>
@@ -31,36 +31,18 @@
     <t>Bpp</t>
   </si>
   <si>
-    <t>Alignment</t>
-  </si>
-  <si>
     <t>GB</t>
   </si>
   <si>
     <t>TouchGFX - Typography Sheet</t>
   </si>
   <si>
-    <t>Text ID</t>
-  </si>
-  <si>
     <t>TouchGFX - Translation Sheet</t>
   </si>
   <si>
     <t>Typography Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Add additional language here (1 to 3 capital letters) - </t>
-  </si>
-  <si>
-    <t>Add additional language here (1 to 3 capital letters) - 2</t>
-  </si>
-  <si>
-    <t>Add additional language here (1 to 3 capital letters) - 3</t>
-  </si>
-  <si>
-    <t>Add additional language here (1 to 3 capital letters) - 4</t>
-  </si>
-  <si>
     <t>Add additional language columns here</t>
   </si>
   <si>
@@ -140,6 +122,114 @@
   </si>
   <si>
     <t>0x22EF</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>0-9</t>
+  </si>
+  <si>
+    <t>&lt;number&gt;</t>
+  </si>
+  <si>
+    <t>Asap-Regular.ttf</t>
+  </si>
+  <si>
+    <t>TEXT ID</t>
+  </si>
+  <si>
+    <t>TYPOGRAPHY NAME</t>
+  </si>
+  <si>
+    <t>ALIGNMENT</t>
+  </si>
+  <si>
+    <t>DIRECTION</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>LTR</t>
+  </si>
+  <si>
+    <t>SingleUseId1</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>SingleUseId2</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>ButtonDown</t>
+  </si>
+  <si>
+    <t>SingleUseId3</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>SingleUseId5</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>SingleUseId6</t>
+  </si>
+  <si>
+    <t>SingleUseId7</t>
+  </si>
+  <si>
+    <t>SingleUseId8</t>
+  </si>
+  <si>
+    <t>Repeat Button</t>
+  </si>
+  <si>
+    <t>Click Button</t>
+  </si>
+  <si>
+    <t>Touch Button</t>
+  </si>
+  <si>
+    <t>-+,.</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>numberText</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>toggleButtonWhite</t>
+  </si>
+  <si>
+    <t>toggleButtonOrange</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Toggle Button (touch text)</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
   </si>
   <si>
     <t>Widget Wildcard Characters</t>
@@ -918,14 +1008,14 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="B3:I799" totalsRowShown="0" tableBorderDxfId="0">
   <tableColumns count="8">
-    <tableColumn id="1" name="Text ID"/>
-    <tableColumn id="2" name="Typography Name"/>
-    <tableColumn id="3" name="Alignment"/>
+    <tableColumn id="1" name="TEXT ID"/>
+    <tableColumn id="2" name="TYPOGRAPHY NAME"/>
+    <tableColumn id="3" name="ALIGNMENT"/>
     <tableColumn id="4" name="GB"/>
-    <tableColumn id="5" name="Add additional language here (1 to 3 capital letters) - "/>
-    <tableColumn id="6" name="Add additional language here (1 to 3 capital letters) - 2"/>
-    <tableColumn id="7" name="Add additional language here (1 to 3 capital letters) - 3"/>
-    <tableColumn id="8" name="Add additional language here (1 to 3 capital letters) - 4"/>
+    <tableColumn id="5" name="DIRECTION"/>
+    <tableColumn id="6" name="Column1"/>
+    <tableColumn id="7" name="Column2"/>
+    <tableColumn id="8" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1332,7 +1422,7 @@
     </row>
     <row r="2" spans="2:16" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -1345,7 +1435,7 @@
     </row>
     <row r="3" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>0</v>
@@ -1357,57 +1447,84 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
       <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
       <c r="J4" s="24"/>
       <c r="L4" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
       <c r="L5" s="7" t="s">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N5" s="9">
         <v>20</v>
@@ -1418,15 +1535,30 @@
       <c r="P5" s="10"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
       <c r="L6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N6" s="9">
         <v>4</v>
@@ -1438,65 +1570,65 @@
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L7" s="7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L8" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P8" s="10"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L9" s="11" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L10" s="11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="P10" s="14"/>
     </row>
@@ -1505,7 +1637,7 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="M12" s="16" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J5"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.28515625" customWidth="1"/>
@@ -1548,7 +1680,7 @@
     </row>
     <row r="2" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -1558,37 +1690,205 @@
       <c r="H2" s="23"/>
       <c r="I2" s="23"/>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
+      <c r="F3" t="s">
+        <v>41</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>
   <mergeCells count="1">
